--- a/excel-files/TAGUIG_PATEROS/SILANGAN ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/TAGUIG_PATEROS/SILANGAN ELEMENTARY SCHOOL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="817" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB243939-B05F-4A12-A40E-8E2240FF1A2E}"/>
+  <xr:revisionPtr revIDLastSave="821" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7846A275-02A7-4721-94FE-5508AB6BAE19}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ADM-SLM" sheetId="5" r:id="rId1"/>
@@ -14906,10 +14906,10 @@
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="26.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" style="45" customWidth="1"/>
+    <col min="2" max="2" width="24.140625" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" customWidth="1"/>
+    <col min="5" max="5" width="17" style="45" customWidth="1"/>
     <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.5703125" customWidth="1"/>
     <col min="8" max="9" width="20.85546875" customWidth="1"/>
